--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -334,7 +334,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Synonyme MOS : typeAutorisation</t>
+    <t>Synonyme : typeAutorisation</t>
   </si>
   <si>
     <t>Extension.extension:type.id</t>
@@ -478,7 +478,7 @@
     <t>The start of the period. The boundary is inclusive.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateDebutAutorisation</t>
+    <t>Synonyme : dateDebutAutorisation</t>
   </si>
   <si>
     <t>Period.start</t>
@@ -503,7 +503,7 @@
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
   </si>
   <si>
-    <t>Synonyme MOS : dateFinAutorisation</t>
+    <t>Synonyme : dateFinAutorisation</t>
   </si>
   <si>
     <t>If the end of the period is missing, it means that the period is ongoing</t>
@@ -524,7 +524,7 @@
     <t>Discipline à laquelle l'autorisation d'exercice est restreinte, le cas échéant.</t>
   </si>
   <si>
-    <t>Synonyme MOS : disciplineAutorisee</t>
+    <t>Synonyme : disciplineAutorisee</t>
   </si>
   <si>
     <t>Extension.extension:field.id</t>
@@ -557,7 +557,7 @@
     <t>Profession pour laquelle l'autorisation est délivrée.</t>
   </si>
   <si>
-    <t>Synonyme MOS : profession</t>
+    <t>Synonyme : profession</t>
   </si>
   <si>
     <t>Extension.extension:profession.id</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
